--- a/SGC-CKN/Excel/78456f92-df31-4fd2-acc6-9bf6aaf12dad_Xã_Cần_Giờ__Thành_phố_Hồ_Chí_Minh_TNB1B152_1200_mm_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/78456f92-df31-4fd2-acc6-9bf6aaf12dad_Xã_Cần_Giờ__Thành_phố_Hồ_Chí_Minh_TNB1B152_1200_mm_14-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="117">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Khu đô thị du lịch lấn biển Cần Giờ</t>
+    <t>Cần Giờ</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -38,16 +38,16 @@
     <t>TNB1B152</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t/>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t>SGCT-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
   </si>
   <si>
-    <t>1200 mm</t>
+    <t>D1200</t>
   </si>
   <si>
     <t>Bắt đầu thi công</t>
@@ -119,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét pha - cát pha màu xám xanh, xám đen, trạng thái dẻo chảy đến chảy</t>
+    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo mềm, dẻo chảy đến chảy</t>
   </si>
   <si>
     <t xml:space="preserve">09:15
@@ -185,7 +185,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét - Sét pha màu xám xanh, xám đen, trạng thái dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">20:50
@@ -219,7 +219,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát hạt mịn màu xám ghi, xám vàng, kết cấu chặt đến rất chặt</t>
+    <t>Cát mịn đến hạt vừa, màu xám ghi, xám vàng, đôi chỗ kẹp sét pha, kết cấu chặt vừa đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">21:50
@@ -398,6 +398,9 @@
   </si>
   <si>
     <t>TỔNG CỘNG</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -2689,10 +2692,10 @@
         <v>115</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="D6" s="21">
         <v>34</v>

--- a/SGC-CKN/Excel/78456f92-df31-4fd2-acc6-9bf6aaf12dad_Xã_Cần_Giờ__Thành_phố_Hồ_Chí_Minh_TNB1B152_1200_mm_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/78456f92-df31-4fd2-acc6-9bf6aaf12dad_Xã_Cần_Giờ__Thành_phố_Hồ_Chí_Minh_TNB1B152_1200_mm_14-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TNB1B152</t>
+    <t>TN-B1-B.152</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/78456f92-df31-4fd2-acc6-9bf6aaf12dad_Xã_Cần_Giờ__Thành_phố_Hồ_Chí_Minh_TNB1B152_1200_mm_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/78456f92-df31-4fd2-acc6-9bf6aaf12dad_Xã_Cần_Giờ__Thành_phố_Hồ_Chí_Minh_TNB1B152_1200_mm_14-03-2026.xlsx
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi</t>
+    <t>Khách sạn GrandHyatt</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>TN-B1-B.152</t>
+    <t>B1.52</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -119,7 +119,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo mềm, dẻo chảy đến chảy</t>
+    <t>Sét pha, cát pha màu xám ghi, xám xanh, xám đen, TT dẻo chảy đến chảy</t>
   </si>
   <si>
     <t xml:space="preserve">09:15
